--- a/docs/충청남도 교육청 태양광 진단 플랫폼_반영점검.xlsx
+++ b/docs/충청남도 교육청 태양광 진단 플랫폼_반영점검.xlsx
@@ -12776,7 +12776,7 @@
       </c>
       <c r="J187" s="74" t="inlineStr">
         <is>
-          <t>반영 · components/solar-edu/JourneyPanel.tsx, EDU_FACTS 롤링</t>
+          <t>반영 · JourneyPanel.tsx · mocks/eduContent.ts 수준별 주제·티커 문구</t>
         </is>
       </c>
       <c r="K187" s="44" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="J188" s="74" t="inlineStr">
         <is>
-          <t>반영 · components/solar-edu/ImpactPanel.tsx, utils/eco.ts</t>
+          <t>반영 · ImpactPanel.tsx, utils/eco.ts · 수준별 환산 항목 3~4종</t>
         </is>
       </c>
       <c r="K188" s="44" t="n"/>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="J189" s="74" t="inlineStr">
         <is>
-          <t>반영 · HeadlineStrip.tsx, EDU_FACTS</t>
+          <t>반영 · 초·중·고 3수준(mocks/eduContent.ts). 학교급 자동 매핑 + ?level= 고정 + 화면 세그먼트로 전환</t>
         </is>
       </c>
       <c r="K189" s="44" t="n"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="J190" s="74" t="inlineStr">
         <is>
-          <t>반영 · GrowingTree.tsx, SunPathArt.tsx</t>
+          <t>반영 · GrowingTree.tsx, SunPathArt.tsx, 초등판 DayStoryPanel.tsx 해 크기 변화</t>
         </is>
       </c>
       <c r="K190" s="44" t="n"/>
@@ -20225,7 +20225,7 @@
       </c>
       <c r="J295" s="74" t="inlineStr">
         <is>
-          <t>반영 · Reports/components/MonthlyTab.tsx 발전소 정보</t>
+          <t>반영 · 보고서 1장(monthly/ReportSheet.tsx) 발전소 정보 표</t>
         </is>
       </c>
       <c r="K295" s="44" t="n"/>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="J296" s="74" t="inlineStr">
         <is>
-          <t>반영 · 같은 화면</t>
+          <t>반영 · 2장 TrendChart — 금월·전월 일별 발전량 곡선</t>
         </is>
       </c>
       <c r="K296" s="44" t="n"/>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="J297" s="74" t="inlineStr">
         <is>
-          <t>반영 · 같은 화면</t>
+          <t>반영 · 2장 InverterHoursChart — 인버터별 일별 발전시간</t>
         </is>
       </c>
       <c r="K297" s="44" t="n"/>
@@ -20435,7 +20435,7 @@
       </c>
       <c r="J298" s="74" t="inlineStr">
         <is>
-          <t>반영 · seriesPalette</t>
+          <t>반영 · seriesPalette 색 + SERIES_DASH 선 모양</t>
         </is>
       </c>
       <c r="K298" s="44" t="n"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="J299" s="74" t="inlineStr">
         <is>
-          <t>반영 · usePrint (브라우저 인쇄 → PDF)</t>
+          <t>반영 · useReportPdf — A4 지면을 장마다 캡처해 PDF 한 장씩 담음. 브라우저 인쇄도 유지</t>
         </is>
       </c>
       <c r="K299" s="44" t="n"/>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="J302" s="74" t="inlineStr">
         <is>
-          <t>반영 · MonthlyTab.tsx 인버터별 AI 진단 결과</t>
+          <t>반영 · 인버터마다 한 장, DiagnosisChart — 일별 정상범위 띠 위에 측정값</t>
         </is>
       </c>
       <c r="K302" s="44" t="n"/>
@@ -20785,7 +20785,7 @@
       </c>
       <c r="J303" s="74" t="inlineStr">
         <is>
-          <t>반영 · 같은 화면 스트링·접속반 단위 진단</t>
+          <t>반영 · 같은 장 StringEfficiencyChart — 회로별 일별 효율(정상범위 88~104%)</t>
         </is>
       </c>
       <c r="K303" s="44" t="n"/>
@@ -20855,7 +20855,7 @@
       </c>
       <c r="J304" s="74" t="inlineStr">
         <is>
-          <t>반영 · 같은 화면</t>
+          <t>반영 · 같은 장 고장분류 표(발생일 묶음)</t>
         </is>
       </c>
       <c r="K304" s="44" t="n"/>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="J306" s="74" t="inlineStr">
         <is>
-          <t>반영 · usePrint</t>
+          <t>반영 · useReportPdf</t>
         </is>
       </c>
       <c r="K306" s="44" t="n"/>
